--- a/public/blog/tenko-kirokubo-template/tenko-kirokubo-template.xlsx
+++ b/public/blog/tenko-kirokubo-template/tenko-kirokubo-template.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="点呼記録簿" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'点呼記録簿'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'点呼記録簿'!$A$1:$Q$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,11 @@
       <name val="Yu Gothic"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="FF666666"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -63,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -85,11 +90,88 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,6 +188,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -507,30 +598,30 @@
           <t>令和　　年　　月　　日（　　）</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="8" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>氏名：</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="8" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>屋号：</t>
         </is>
       </c>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
-      <c r="P2" s="3" t="n"/>
-      <c r="Q2" s="3" t="n"/>
+      <c r="N2" s="7" t="n"/>
+      <c r="O2" s="7" t="n"/>
+      <c r="P2" s="7" t="n"/>
+      <c r="Q2" s="8" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -543,28 +634,28 @@
           <t>業務前点呼</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="8" t="n"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>業務後点呼</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="4" t="n"/>
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
+      <c r="N3" s="7" t="n"/>
+      <c r="O3" s="7" t="n"/>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="8" t="n"/>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="4" t="n"/>
+      <c r="A4" s="9" t="n"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
           <t>実施
@@ -1140,18 +1231,35 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>delilog - 軽貨物ドライバー向け業務記録アプリ　この記録簿は、スマホアプリでも付けられます（無料）</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>https://delilog.app</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
+    <mergeCell ref="A15:I15"/>
     <mergeCell ref="M2:Q2"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="A12:Q12"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A12:Q12"/>
+    <mergeCell ref="J15:Q15"/>
     <mergeCell ref="F2:L2"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A13:Q13"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/public/blog/tenko-kirokubo-template/tenko-kirokubo-template.xlsx
+++ b/public/blog/tenko-kirokubo-template/tenko-kirokubo-template.xlsx
@@ -1234,7 +1234,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>delilog - 軽貨物ドライバー向け業務記録アプリ　この記録簿は、スマホアプリでも付けられます（無料）</t>
+          <t>delilog - 軽貨物ドライバー向け業務記録アプリ</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
